--- a/samples/ss_krian12_gresik_ingest.xlsx
+++ b/samples/ss_krian12_gresik_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">

--- a/samples/ss_krian12_gresik_ingest.xlsx
+++ b/samples/ss_krian12_gresik_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U54"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Krian 500/150 kV</t>
+          <t>IBT 1 Krian 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GITET Gresik</t>
+          <t>IBT 2 Krian 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GRSIK7</t>
+          <t>IBT 2 KRIAN7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>500 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>KRIAN7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SBRAT5</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -791,51 +805,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 1,2 Gresik 500/150 kV</t>
+          <t>GITET Gresik</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 1 GRSIK7</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>GRSIK7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>GRSIK5</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -845,14 +841,10 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -866,37 +858,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Surabaya Barat (bus 150 kV)</t>
+          <t>IBT 1 Gresik 500/150 kV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SBRAT5</t>
+          <t>IBT 1 GRSIK7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GRSIK7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>GRSIK5</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>seksi A</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -906,10 +908,14 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -923,31 +929,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gresik (bus 150 kV)</t>
+          <t>IBT 2 Gresik 500/150 kV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>IBT 2 GRSIK7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>GRSIK7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>GRSIK5</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -959,10 +979,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -976,12 +1000,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gresik Lama</t>
+          <t>Surabaya Barat (bus 150 kV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GRLMA</t>
+          <t>SBRAT5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1002,7 +1026,11 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>seksi A</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -1029,17 +1057,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLTU Gresik</t>
+          <t>Gresik (bus 150 kV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KIT_GRESIK</t>
+          <t>GRSIK5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1082,12 +1110,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kalang</t>
+          <t>Gresik Lama</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KLANG</t>
+          <t>GRLMA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1096,7 +1124,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1118,14 +1146,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1139,21 +1163,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Darmo</t>
+          <t>PLTU Gresik</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DARMO</t>
+          <t>KIT_GRESIK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1175,14 +1199,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1196,12 +1216,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tandes</t>
+          <t>Kalang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TNDES</t>
+          <t>KLANG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1237,7 +1257,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5;6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1253,12 +1273,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Altap</t>
+          <t>Darmo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ALTAP</t>
+          <t>DARMO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1289,10 +1309,14 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1306,12 +1330,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Segoromadu</t>
+          <t>Tandes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SGMDU</t>
+          <t>TNDES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1332,11 +1356,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>seksi B</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1346,10 +1366,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5;6</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1363,12 +1387,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sukorejo Kreb</t>
+          <t>Altap</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SKREP</t>
+          <t>ALTAP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1399,14 +1423,10 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1420,12 +1440,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wilmar</t>
+          <t>Segoromadu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WLMAR</t>
+          <t>SGMDU</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1446,7 +1466,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>seksi B</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
@@ -1456,14 +1480,10 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1477,12 +1497,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bambe</t>
+          <t>Sukorejo Kreb</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BAMBE</t>
+          <t>SKREP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1491,7 +1511,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1518,7 +1538,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1534,12 +1554,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Suwahan</t>
+          <t>Wilmar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SWHAN</t>
+          <t>WLMAR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1548,7 +1568,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1575,7 +1595,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>8;9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1591,12 +1611,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pakem Mia</t>
+          <t>Bambe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PKMIA</t>
+          <t>BAMBE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1632,7 +1652,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1648,12 +1668,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Perak</t>
+          <t>Suwahan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PERAK</t>
+          <t>SWHAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1689,7 +1709,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8;9</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1705,12 +1725,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kepatihan</t>
+          <t>Pakem Mia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KPANG</t>
+          <t>PKMIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1719,7 +1739,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1741,10 +1761,14 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1758,12 +1782,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Undaan</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UDAAN</t>
+          <t>PERAK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1772,7 +1796,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1794,10 +1818,14 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1811,12 +1839,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karangbanan</t>
+          <t>Kepatihan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KRBAN</t>
+          <t>KPANG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1847,14 +1875,10 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1868,12 +1892,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gunungsari</t>
+          <t>Undaan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GNSRI</t>
+          <t>UDAAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1921,12 +1945,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ujung</t>
+          <t>Karangbanan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UJUNG</t>
+          <t>KRBAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1962,7 +1986,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -1978,12 +2002,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Petrokimia</t>
+          <t>Gunungsari</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PTISM</t>
+          <t>GNSRI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2031,12 +2055,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rungkut</t>
+          <t>Ujung</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RNKUT</t>
+          <t>UJUNG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2045,7 +2069,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2057,11 +2081,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>seksi A/B</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
@@ -2071,10 +2091,14 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2088,12 +2112,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gubeng</t>
+          <t>Petrokimia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GBONG</t>
+          <t>PTISM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2102,7 +2126,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2124,14 +2148,10 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2145,12 +2165,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Waru (bus 150 kV)</t>
+          <t>Rungkut</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WARU5</t>
+          <t>RNKUT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2171,7 +2191,11 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>seksi A/B</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
@@ -2198,12 +2222,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Surabaya Selatan</t>
+          <t>Gubeng</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SBSEL</t>
+          <t>GBONG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2212,7 +2236,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2234,10 +2258,14 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2251,12 +2279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sukolilo</t>
+          <t>Waru (bus 150 kV)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SLILO</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2265,7 +2293,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2287,14 +2315,10 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2308,12 +2332,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hayam Jaya</t>
+          <t>Surabaya Selatan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HJAYA</t>
+          <t>SBSEL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2361,12 +2385,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Buduran (bus 150 kV)</t>
+          <t>Sukolilo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BDRAN5</t>
+          <t>SLILO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2402,7 +2426,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>13;14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2418,17 +2442,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Waru</t>
+          <t>Hayam Jaya</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IBT 1 WARU5</t>
+          <t>HJAYA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2436,33 +2460,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>WARU5</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>WARU4</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
@@ -2489,12 +2495,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Waru (bus 70 kV)</t>
+          <t>Buduran (bus 150 kV)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WARU4</t>
+          <t>BDRAN5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2507,7 +2513,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2525,10 +2531,14 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>13;14</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2542,17 +2552,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jawa Steel</t>
+          <t>IBT 150/70 kV Waru</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JSTEL</t>
+          <t>IBT 1 WARU5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2560,15 +2570,33 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>WARU5</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>WARU4</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
@@ -2595,12 +2623,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Waru (bus 70 kV)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KSARI</t>
+          <t>WARU4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2609,11 +2637,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2648,12 +2676,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wonokromo</t>
+          <t>Jawa Steel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WKRMO</t>
+          <t>JSTEL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2662,7 +2690,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2701,12 +2729,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nganggel</t>
+          <t>Kesari</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NGGEL</t>
+          <t>KSARI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2737,14 +2765,10 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2758,12 +2782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kejuron</t>
+          <t>Wonokromo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KJRAN</t>
+          <t>WKRMO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2811,17 +2835,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IBT 1,7 Buduran 150/70 kV</t>
+          <t>Nganggel</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IBT 1 BDRAN5</t>
+          <t>NGGEL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2829,33 +2853,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>BDRAN5</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>BDRAN</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>IBT 1 dan 7</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
@@ -2870,7 +2876,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -2886,12 +2892,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Buduran (bus 70 kV)</t>
+          <t>Kejuron</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BDRAN</t>
+          <t>KJRAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2904,7 +2910,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2939,17 +2945,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New Buduran</t>
+          <t>IBT 1 Buduran 150/70 kV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NBRAN5</t>
+          <t>IBT 1 BDRAN5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2957,13 +2963,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>BDRAN5</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BDRAN</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -2975,10 +2995,14 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2992,31 +3016,45 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Simpang</t>
+          <t>IBT 7 Buduran 150/70 kV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SIMPG</t>
+          <t>IBT 7 BDRAN5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BDRAN5</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BDRAN</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -3028,10 +3066,14 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3045,12 +3087,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sidoarjo</t>
+          <t>Buduran (bus 70 kV)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SDRJO</t>
+          <t>BDRAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3059,11 +3101,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -3098,12 +3140,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sedati</t>
+          <t>New Buduran</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SDATI</t>
+          <t>NBRAN5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3112,11 +3154,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -3151,12 +3193,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mpion</t>
+          <t>Simpang</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MPION</t>
+          <t>SIMPG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3169,7 +3211,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -3187,14 +3229,10 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3208,12 +3246,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kedinding</t>
+          <t>Sidoarjo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KDING</t>
+          <t>SDRJO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3244,14 +3282,10 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>22;23</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3265,12 +3299,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gelam Ur</t>
+          <t>Sedati</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GLMUR</t>
+          <t>SDATI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3279,11 +3313,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -3301,14 +3335,10 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3322,12 +3352,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bangkalan</t>
+          <t>Mpion</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BKLAN</t>
+          <t>MPION</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3336,11 +3366,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3348,11 +3378,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>seksi A/B</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
@@ -3367,7 +3393,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>21;22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -3383,12 +3409,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sampang</t>
+          <t>Kedinding</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SAMPG</t>
+          <t>KDING</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3397,7 +3423,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3424,7 +3450,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22;23</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -3440,12 +3466,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pamekasan</t>
+          <t>Gelam Ur</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PKSAN</t>
+          <t>GLMUR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3454,7 +3480,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3481,7 +3507,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -3497,12 +3523,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Guluk-Guluk</t>
+          <t>Bangkalan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GULUK</t>
+          <t>BKLAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3511,7 +3537,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3523,7 +3549,11 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>seksi A/B</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
@@ -3538,7 +3568,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21;22</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -3554,12 +3584,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sumenep</t>
+          <t>Sampang</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SMNEP</t>
+          <t>SAMPG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3568,7 +3598,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3590,16 +3620,187 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pamekasan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PKSAN</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Guluk-Guluk</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GULUK</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>11</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sumenep</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SMNEP</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6795,12 +6996,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] Kopel 150 kV GI Sawahan dibuka untuk spliting SS Kriandan SS Gresik</t>
+          <t>[BELUM_DITETAPKAN] Kopel 150 kV GI Sawahan dibuka untuk spliting SS Kriandan SS Gresik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6970,12 +7171,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[N-1] GI 150 kV Buduran hanya single bus</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV Buduran hanya single bus</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7005,12 +7206,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV Maspion hanya beroperasi single Busbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Maspion hanya beroperasi single Busbar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7110,12 +7311,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[N-1] Terdapat Bottleneck di Pht 150 kV GIS Ujung Bay Tandes dengan deklarasi 850A , Pht 150 kV GIS Ujung Bay perak dengan deklarasi 900A. Pembebanan SUTT 150 kV Tandes-Perak dan Tandes-Ujung sudah &gt;85%</t>
+          <t>[BELUM_DITETAPKAN] Terdapat Bottleneck di Pht 150 kV GIS Ujung Bay Tandes dengan deklarasi 850A , Pht 150 kV GIS Ujung Bay perak dengan deklarasi 900A. Pembebanan SUTT 150 kV Tandes-Perak dan Tandes-Ujung sudah &gt;85%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7145,12 +7346,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[N-1] GI 150 kV Perak Hanya Single Busbar dan single phi arah Tandes dan arah Ujung sehingga kurang andal dalam pengoperasiannya</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV Perak Hanya Single Busbar dan single phi arah Tandes dan arah Ujung sehingga kurang andal dalam pengoperasiannya</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -7215,12 +7416,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[N-1] Kopel 150 kV GI Bangkalan dibuka untuk spliting SS Krian dan SS Gresik</t>
+          <t>[BELUM_DITETAPKAN] Kopel 150 kV GI Bangkalan dibuka untuk spliting SS Krian dan SS Gresik</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -7285,12 +7486,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Bangkalan-Sampang berbeban&gt;100%</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Bangkalan-Sampang berbeban&gt;100%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -7320,12 +7521,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Sampang - Pamekasanberbeban &gt;65%</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Sampang - Pamekasanberbeban &gt;65%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7355,12 +7556,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi Drop tegangan di Subsistem Gresik 1,2 pada GI 150 kV Kenjeran, dan GI 150 kV Guluk- Guluk</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di Subsistem Gresik 1,2 pada GI 150 kV Kenjeran, dan GI 150 kV Guluk- Guluk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
